--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/ALABAMA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/ALABAMA_2024.xlsx
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C142">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C164">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C255">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Huehuetl</t>
+          <t>Huehuetla</t>
         </is>
       </c>
       <c r="C358">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C360">
